--- a/data-raw/data-tidy/public-site/moa-machine-county/xlsx/case-year-2023-batch03.xlsx
+++ b/data-raw/data-tidy/public-site/moa-machine-county/xlsx/case-year-2023-batch03.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">上海</t>
   </si>
   <si>
-    <t xml:space="preserve">鲜食葡萄</t>
+    <t xml:space="preserve">葡萄</t>
   </si>
   <si>
     <t xml:space="preserve">茶叶</t>
